--- a/data/trans_orig/KIDM_C_2_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_2_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>53273</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114246</t>
+          <t>114161</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>15983</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41053</t>
+          <t>41258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45692</t>
+          <t>45710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16976</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>30654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>547</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15182</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34084</t>
+          <t>34227</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>38818</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>773</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>22834</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39071</t>
+          <t>39049</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45409</t>
+          <t>45368</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65081</t>
+          <t>64379</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>72091</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76712</t>
+          <t>76632</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>140169</t>
+          <t>140211</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>200011</t>
+          <t>199979</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>208375</t>
+          <t>208436</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>260071</t>
+          <t>259755</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>269297</t>
+          <t>269356</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>463375</t>
+          <t>463707</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>475939</t>
+          <t>475957</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
